--- a/data/mapas/Mapa_de_Carrera_Ingles.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ingles.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B75, "SI")</f>
+        <f>COUNTIF(B6:B45, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C75, "SI")</f>
+        <f>COUNTIF(C6:C45, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F75, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F45, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Fonética Y Fonología I</t>
+          <t>Lengua Inglesa I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B75, "SI")/64</f>
+        <f>COUNTIF(B6:B45, "SI")/36</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Geografía. Y Cultura DE LAS ISLAS Británicas</t>
+          <t>Fonética y Fonología Inglesa I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C75, "SI")/64</f>
+        <f>COUNTIF(C6:C45, "SI")/36</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Geografía. Y Cultura. DE EE.UU</t>
+          <t>Gramática Inglesa I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Geografía. Y CULTURA DE LAS ISLAS BRIT. (1º C)</t>
+          <t>Dicción y Práctica de Laboratorio I</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Geografía. Y CULTURA DE LOS EE.UU.. (1ºC)</t>
+          <t>Geografía y Cultura de los Pueblos de Habla Inglesa I</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Geografía Y CULTURA DE LAS I. Británicas</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Gramática INGLESA I</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario I</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -987,37 +987,10 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Inglesa I</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>1° Año</t>
-        </is>
-      </c>
-      <c r="E14" s="10">
-        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1028,7 +1001,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Lengua Inglesa II</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1043,7 +1016,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1067,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Práctica EN LABORATORIO DE IDIOMAS I</t>
+          <t>Fonética y Fonología Inglesa II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1082,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1101,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Práctica EN LABORATORIO I</t>
+          <t>Gramática Inglesa II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1116,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1135,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Psicología EDUCACIONAL</t>
+          <t>Literatura en Lengua Inglesa I</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1150,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1169,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de Nivel</t>
+          <t>Geografía y Cultura de los Pueblos de Habla Inglesa II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1184,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1203,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos del Nivel</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1218,7 +1191,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E20" s="10">
@@ -1237,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1252,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1268,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos de la Educación</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Análisis DEL DISCURSO</t>
+          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario II y Residencia</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1309,44 +1309,17 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica Docente. en Nivel Inicial y Primario I</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E24" s="10">
-        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G24" s="11">
-        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica DocenteN INIC. Y PRIM I</t>
+          <t>Lengua Inglesa III</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1361,7 +1334,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1380,7 +1353,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica GENERAL</t>
+          <t>Fonología y Fonética Inglesa III</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1395,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1414,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Fonética Y Fonología II</t>
+          <t>Gramática Inglesa III</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1429,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1448,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Gramática INGLESA II</t>
+          <t>Lingüística General y Aplicada</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1463,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1482,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Civilizacion Inglesa I</t>
+          <t>Literatura en Lengua Inglesa II</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1497,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1516,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Lengua Inglesa II</t>
+          <t>Historia de la Lengua Inglesa</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1531,7 +1504,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E30" s="10">
@@ -1550,7 +1523,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Literatura Inglesa I</t>
+          <t>Didáctica Especial y Construcción de la Práctica Docente en Nivel Medio I</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1565,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1584,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Práctica EN LABORATORIO DE IDIOMAS II</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1599,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1618,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica EN LABORATORIO II</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1633,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1649,51 +1622,51 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo de Campo II</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E34" s="10">
-        <f>IF(B34="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>IF(C34="SI", "APROBADO", IF(B34="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G34" s="11">
-        <f>IF(C34="SI", "🟢 Aprobada", IF(B34="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Inglesa IV</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Adquisición de la Lengua Materna</t>
+          <t>Análisis del Discurso en Lengua Inglesa</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1708,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1727,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente. en Nivel Inicial y Primario II y Residencia</t>
+          <t>Literatura en Lengua Inglesa III y Contemporánea</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1742,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1761,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente. en Nivel Medio I</t>
+          <t>Estudios Culturales Anglófonos</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1776,7 +1749,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1795,7 +1768,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente EN en Nivel Medio I</t>
+          <t>Didáctica Especial y Residencia en Nivel Medio y Superior</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1810,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1829,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Educación SEXUAL INTEGRAL</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1844,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1863,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Filosofía</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1878,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1894,44 +1867,17 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Fonología EN Laboratorio. Y SU DIDATICA I</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E42" s="10">
-        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G42" s="11">
-        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Fonología EN LABORATORIO Y SU DIDAC. I</t>
+          <t>Seminario de Literatura en Lengua Inglesa</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1946,7 +1892,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E43" s="10">
@@ -1965,7 +1911,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Historia. DE LA CIVILIZACION INGLESA II</t>
+          <t>Seminario de Lingüística y Adquisición del Lenguaje</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1980,7 +1926,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E44" s="10">
@@ -1999,7 +1945,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Historia Norteamericana</t>
+          <t>Taller de Traducción y Práctica Profesional</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -2014,7 +1960,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E45" s="10">
@@ -2030,940 +1976,26 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Introduccion a la Lingüística</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Inglesa III</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Inglesa II</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica Docente. en Nivel Medio II y Residencia</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Derechos Humanos, SOCIEDAD Y ESTADO</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Fonología EN Laboratorio. Y Didáctica II</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>HISTORIA DE LA Educación ARGENTINA</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Inglesa IV</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Contemporanea</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E55" s="10">
-        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G55" s="11">
-        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Inglesa III</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E56" s="10">
-        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F56" s="10">
-        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G56" s="11">
-        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Literatura Norteamericana</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E57" s="10">
-        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F57" s="10">
-        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G57" s="11">
-        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>SISTEMA Y Política Educativa (cuatr.)</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E58" s="10">
-        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F58" s="10">
-        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G58" s="11">
-        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>Fonología EN Laboratorio. Y SU Didáctica. II</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E60" s="10">
-        <f>IF(B60="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F60" s="10">
-        <f>IF(C60="SI", "APROBADO", IF(B60="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G60" s="11">
-        <f>IF(C60="SI", "🟢 Aprobada", IF(B60="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA: Francés NIVEL I</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E61" s="10">
-        <f>IF(B61="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F61" s="10">
-        <f>IF(C61="SI", "APROBADO", IF(B61="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G61" s="11">
-        <f>IF(C61="SI", "🟢 Aprobada", IF(B61="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>Metod. de la Invest. en Lenguas Extr</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E62" s="10">
-        <f>IF(B62="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F62" s="10">
-        <f>IF(C62="SI", "APROBADO", IF(B62="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G62" s="11">
-        <f>IF(C62="SI", "🟢 Aprobada", IF(B62="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E64" s="10">
-        <f>IF(B64="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F64" s="10">
-        <f>IF(C64="SI", "APROBADO", IF(B64="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G64" s="11">
-        <f>IF(C64="SI", "🟢 Aprobada", IF(B64="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E65" s="10">
-        <f>IF(B65="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F65" s="10">
-        <f>IF(C65="SI", "APROBADO", IF(B65="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G65" s="11">
-        <f>IF(C65="SI", "🟢 Aprobada", IF(B65="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>Práctica de Nivel Superior II</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E66" s="10">
-        <f>IF(B66="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F66" s="10">
-        <f>IF(C66="SI", "APROBADO", IF(B66="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G66" s="11">
-        <f>IF(C66="SI", "🟢 Aprobada", IF(B66="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>Acreditación de Residencia Superior</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E67" s="10">
-        <f>IF(B67="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F67" s="10">
-        <f>IF(C67="SI", "APROBADO", IF(B67="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G67" s="11">
-        <f>IF(C67="SI", "🟢 Aprobada", IF(B67="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>El Uso de la Voz en el Aula</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E69" s="10">
-        <f>IF(B69="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F69" s="10">
-        <f>IF(C69="SI", "APROBADO", IF(B69="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G69" s="11">
-        <f>IF(C69="SI", "🟢 Aprobada", IF(B69="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>Fonología EN Laboratorio. Y SU Didáctica. I</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E70" s="10">
-        <f>IF(B70="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F70" s="10">
-        <f>IF(C70="SI", "APROBADO", IF(B70="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G70" s="11">
-        <f>IF(C70="SI", "🟢 Aprobada", IF(B70="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>Geografía DE LAS ISLAS Británicas</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E71" s="10">
-        <f>IF(B71="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F71" s="10">
-        <f>IF(C71="SI", "APROBADO", IF(B71="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G71" s="11">
-        <f>IF(C71="SI", "🟢 Aprobada", IF(B71="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Lectura Escritura y Oralidad I</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E72" s="10">
-        <f>IF(B72="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F72" s="10">
-        <f>IF(C72="SI", "APROBADO", IF(B72="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G72" s="11">
-        <f>IF(C72="SI", "🟢 Aprobada", IF(B72="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA NIVEL I - Francés</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E73" s="10">
-        <f>IF(B73="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F73" s="10">
-        <f>IF(C73="SI", "APROBADO", IF(B73="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G73" s="11">
-        <f>IF(C73="SI", "🟢 Aprobada", IF(B73="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Redaccion del Discurso Academico</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E74" s="10">
-        <f>IF(B74="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F74" s="10">
-        <f>IF(C74="SI", "APROBADO", IF(B74="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G74" s="11">
-        <f>IF(C74="SI", "🟢 Aprobada", IF(B74="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>SISTEMA Y Política Educativa</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E75" s="10">
-        <f>IF(B75="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F75" s="10">
-        <f>IF(C75="SI", "APROBADO", IF(B75="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G75" s="11">
-        <f>IF(C75="SI", "🟢 Aprobada", IF(B75="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="15">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="I12:J12"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A49:G49"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B50 B51 B52 B53 B54 B55 B56 B57 B58 B60 B61 B62 B64 B65 B66 B67 B69 B70 B71 B72 B73 B74 B75 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C50 C51 C52 C53 C54 C55 C56 C57 C58 C60 C61 C62 C64 C65 C66 C67 C69 C70 C71 C72 C73 C74 C75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B43 B44 B45 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C31 C32 C33 C35 C36 C37 C38 C39 C40 C41 C43 C44 C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Ingles.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ingles.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B45, "SI")</f>
+        <f>COUNTIF(B6:B74, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C45, "SI")</f>
+        <f>COUNTIF(C6:C74, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F45, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F74, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B45, "SI")/36</f>
+        <f>COUNTIF(B6:B74, "SI")/65</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Fonética y Fonología Inglesa I</t>
+          <t>Gramática Inglesa I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C45, "SI")/36</f>
+        <f>COUNTIF(C6:C74, "SI")/65</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Gramática Inglesa I</t>
+          <t>Fonética y Fonología I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Dicción y Práctica de Laboratorio I</t>
+          <t>Prácticas en el Laboratorio de Idiomas I</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Geografía y Cultura de los Pueblos de Habla Inglesa I</t>
+          <t>Geografía y Cultura de las Islas Británicas</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Geografía y Cultura de los EEUU y Otros Pueblos de Habla Inglesa</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario I</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -987,10 +987,37 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos de Nivel</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E14" s="10">
+        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Lengua Inglesa II</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1040,7 +1067,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Fonética y Fonología Inglesa II</t>
+          <t>Trabajo de campo I</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1055,7 +1082,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1071,44 +1098,17 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Gramática Inglesa II</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E17" s="10">
-        <f>IF(B17="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>IF(C17="SI", "APROBADO", IF(B17="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="11">
-        <f>IF(C17="SI", "🟢 Aprobada", IF(B17="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Literatura en Lengua Inglesa I</t>
+          <t>Lengua Inglesa II</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Geografía y Cultura de los Pueblos de Habla Inglesa II</t>
+          <t>Gramática Inglesa II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Fonética y Fonología II</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Prácticas en el Laboratorio de Idiomas II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Historia de la Civilización Inglesa I</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente en Nivel Inicial y Primario II y Residencia</t>
+          <t>Literatura Inglesa I</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1309,17 +1309,44 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica General</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E24" s="10">
+        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Lengua Inglesa III</t>
+          <t>Análisis del Discurso</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Fonología y Fonética Inglesa III</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1387,7 +1414,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Gramática Inglesa III</t>
+          <t>Construcción de la Práctica Docente en los Niveles Inicial y Primario I</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1402,7 +1429,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1418,44 +1445,17 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Lingüística General y Aplicada</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E28" s="10">
-        <f>IF(B28="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F28" s="10">
-        <f>IF(C28="SI", "APROBADO", IF(B28="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G28" s="11">
-        <f>IF(C28="SI", "🟢 Aprobada", IF(B28="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Literatura en Lengua Inglesa II</t>
+          <t>Lengua Inglesa III</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Lengua Inglesa</t>
+          <t>Fonología en Laboratorio y Su Didáctica I</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Didáctica Especial y Construcción de la Práctica Docente en Nivel Medio I</t>
+          <t>Historia de la Civilización Inglesa II</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Literatura Inglesa II</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Historia Norteamericana</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1622,17 +1622,44 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E34" s="10">
+        <f>IF(B34="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>IF(C34="SI", "APROBADO", IF(B34="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
+        <f>IF(C34="SI", "🟢 Aprobada", IF(B34="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Lengua Inglesa IV</t>
+          <t>Adquisición de la Lengua Materna y Extranjera</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Análisis del Discurso en Lengua Inglesa</t>
+          <t>Construcción de la Práctica Docente en el Nivel medio I</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1700,7 +1727,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Literatura en Lengua Inglesa III y Contemporánea</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1715,7 +1742,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1734,7 +1761,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Estudios Culturales Anglófonos</t>
+          <t>Construcción de la Práctica docente en los Niveles Inicial y Primario II y Residencia</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1749,7 +1776,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1768,7 +1795,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Didáctica Especial y Residencia en Nivel Medio y Superior</t>
+          <t>Introducción a la Lingüística</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1783,7 +1810,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1799,44 +1826,17 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Educación Sexual Integral (ESI)</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E40" s="10">
-        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F40" s="10">
-        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G40" s="11">
-        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Lengua Inglesa IV</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1867,17 +1867,44 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Literatura Inglesa III</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Literatura en Lengua Inglesa</t>
+          <t>Literatura Contemporánea en Lengua Inglesa</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1892,7 +1919,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E43" s="10">
@@ -1911,7 +1938,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Lingüística y Adquisición del Lenguaje</t>
+          <t>Fonología en Laboratorio y su Didáctica II</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1926,7 +1953,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E44" s="10">
@@ -1945,7 +1972,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Taller de Traducción y Práctica Profesional</t>
+          <t>Literatura Norteamericana</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -1960,7 +1987,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E45" s="10">
@@ -1976,26 +2003,985 @@
         <v/>
       </c>
     </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la Educación Argentina</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Sistema y Política Educativa</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>DDHH, Sociedad y Estado</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente en el Nivel Medio II y Residencia</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Metodología de la Investigación en Lenguas Extranjeras</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Escritura Académica</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E52" s="10">
+        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente en el Nivel Superior y Residencia</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Extranjera Nivel I</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E54" s="10">
+        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F54" s="10">
+        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="11">
+        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Lengua Extranjera Nivel II</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E55" s="10">
+        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F55" s="10">
+        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="11">
+        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Prerrequisitos</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E56" s="10">
+        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F56" s="10">
+        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G56" s="11">
+        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Nuevas Tecnologías</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E57" s="10">
+        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F57" s="10">
+        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G57" s="11">
+        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Taller formativo docente I</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E58" s="10">
+        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F58" s="10">
+        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="11">
+        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>El Texto Literario en el Aula</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E59" s="10">
+        <f>IF(B59="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F59" s="10">
+        <f>IF(C59="SI", "APROBADO", IF(B59="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G59" s="11">
+        <f>IF(C59="SI", "🟢 Aprobada", IF(B59="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Saberes Lúdicos, Motores y Corporales</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E60" s="10">
+        <f>IF(B60="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F60" s="10">
+        <f>IF(C60="SI", "APROBADO", IF(B60="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G60" s="11">
+        <f>IF(C60="SI", "🟢 Aprobada", IF(B60="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Historia Contemporánea de los Pueblos Angloparlantes</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E61" s="10">
+        <f>IF(B61="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F61" s="10">
+        <f>IF(C61="SI", "APROBADO", IF(B61="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G61" s="11">
+        <f>IF(C61="SI", "🟢 Aprobada", IF(B61="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Literaturas en Lengua Inglesa</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E62" s="10">
+        <f>IF(B62="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F62" s="10">
+        <f>IF(C62="SI", "APROBADO", IF(B62="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G62" s="11">
+        <f>IF(C62="SI", "🟢 Aprobada", IF(B62="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>El Profesor de Inglés y el Maestro de Grado / Sala</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E63" s="10">
+        <f>IF(B63="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F63" s="10">
+        <f>IF(C63="SI", "APROBADO", IF(B63="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G63" s="11">
+        <f>IF(C63="SI", "🟢 Aprobada", IF(B63="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Taller formativo docente II</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E64" s="10">
+        <f>IF(B64="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F64" s="10">
+        <f>IF(C64="SI", "APROBADO", IF(B64="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G64" s="11">
+        <f>IF(C64="SI", "🟢 Aprobada", IF(B64="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Alfabetización</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E65" s="10">
+        <f>IF(B65="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F65" s="10">
+        <f>IF(C65="SI", "APROBADO", IF(B65="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G65" s="11">
+        <f>IF(C65="SI", "🟢 Aprobada", IF(B65="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>El Uso de la Voz en el Aula</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E66" s="10">
+        <f>IF(B66="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F66" s="10">
+        <f>IF(C66="SI", "APROBADO", IF(B66="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G66" s="11">
+        <f>IF(C66="SI", "🟢 Aprobada", IF(B66="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Escritura Creativa</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E67" s="10">
+        <f>IF(B67="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F67" s="10">
+        <f>IF(C67="SI", "APROBADO", IF(B67="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G67" s="11">
+        <f>IF(C67="SI", "🟢 Aprobada", IF(B67="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Técnicas Teatrales en el Aula de Inglés</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E68" s="10">
+        <f>IF(B68="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F68" s="10">
+        <f>IF(C68="SI", "APROBADO", IF(B68="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G68" s="11">
+        <f>IF(C68="SI", "🟢 Aprobada", IF(B68="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Redacción del Discurso Académico</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E69" s="10">
+        <f>IF(B69="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F69" s="10">
+        <f>IF(C69="SI", "APROBADO", IF(B69="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G69" s="11">
+        <f>IF(C69="SI", "🟢 Aprobada", IF(B69="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Taller de Didáctica Específica</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E70" s="10">
+        <f>IF(B70="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F70" s="10">
+        <f>IF(C70="SI", "APROBADO", IF(B70="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G70" s="11">
+        <f>IF(C70="SI", "🟢 Aprobada", IF(B70="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Multimedios Aplicados a la Enseñanza del Inglés</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E71" s="10">
+        <f>IF(B71="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F71" s="10">
+        <f>IF(C71="SI", "APROBADO", IF(B71="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G71" s="11">
+        <f>IF(C71="SI", "🟢 Aprobada", IF(B71="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Enseñanza de las Lenguas Extranjeras en Educación Especial</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E72" s="10">
+        <f>IF(B72="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F72" s="10">
+        <f>IF(C72="SI", "APROBADO", IF(B72="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G72" s="11">
+        <f>IF(C72="SI", "🟢 Aprobada", IF(B72="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Técnicas Informáticas Aplicadas a la Enseñanza de la Lengua Extranjera</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E73" s="10">
+        <f>IF(B73="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F73" s="10">
+        <f>IF(C73="SI", "APROBADO", IF(B73="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G73" s="11">
+        <f>IF(C73="SI", "🟢 Aprobada", IF(B73="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>Dinámica de Grupos</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E74" s="10">
+        <f>IF(B74="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F74" s="10">
+        <f>IF(C74="SI", "APROBADO", IF(B74="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G74" s="11">
+        <f>IF(C74="SI", "🟢 Aprobada", IF(B74="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I14:J14"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A42:G42"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B43 B44 B45 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C31 C32 C33 C35 C36 C37 C38 C39 C40 C41 C43 C44 C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B41 B42 B43 B44 B45 B46 B47 B48 B49 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C41 C42 C43 C44 C45 C46 C47 C48 C49 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
